--- a/outputs/daily/hr_rankings_2026-09-29_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-29_full.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14384,7 +14384,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -23054,7 +23054,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -24442,7 +24442,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -26382,7 +26382,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
